--- a/workbooks/professor_master.xlsx
+++ b/workbooks/professor_master.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Master</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:46:20Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:46:20Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:53:15Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:53:15Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -85,7 +85,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:Y13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -215,6 +215,1530 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="0">
+        <is>
+          <t>Chen Wei</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="0">
+        <is>
+          <t>pekingchenwei@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1458/9457.htm</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="0">
+        <is>
+          <t>Database; data mining</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="0">
+        <is>
+          <t>database; data mining; big data</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1458/9457.htm</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="0">
+        <is>
+          <t>Chenren Xu</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="0">
+        <is>
+          <t>chenren@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1504/6954.htm</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr" s="0">
+        <is>
+          <t>Wireless networking from the system perspective</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr" s="0">
+        <is>
+          <t>wireless networking; mobile systems; networking</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1504/6954.htm</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; title normalized from page summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="0">
+        <is>
+          <t>Hao Dan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="0">
+        <is>
+          <t>haodan@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1502/6746.htm</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr" s="0">
+        <is>
+          <t>Software engineering; software testing</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr" s="0">
+        <is>
+          <t>software engineering; software testing; debugging; maintenance</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1502/6746.htm</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr" s="0">
+        <is>
+          <t>Huang Gang</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr" s="0">
+        <is>
+          <t>hg@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1502/6736.htm</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr" s="0">
+        <is>
+          <t>System software; software architecture</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr" s="0">
+        <is>
+          <t>system software; software architecture; cloud computing; IoT</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1502/6736.htm</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr" s="0">
+        <is>
+          <t>Jiang Tingting</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr" s="0">
+        <is>
+          <t>ttjiang@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1503/6705.htm</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr" s="0">
+        <is>
+          <t>Computer vision; image and video quality assessment</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr" s="0">
+        <is>
+          <t>computer vision; image quality; video quality</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1503/6705.htm</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr" s="0">
+        <is>
+          <t>Li Wenxin</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr" s="0">
+        <is>
+          <t>lwx@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1500/6768.htm</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr" s="0">
+        <is>
+          <t>Biometrics; image processing; pattern recognition; content-based image retrieval</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr" s="0">
+        <is>
+          <t>biometrics; image processing; pattern recognition; CBIR</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1500/6768.htm</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr" s="0">
+        <is>
+          <t>Sun Yanchun</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr" s="0">
+        <is>
+          <t>sunyc@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1502/6727.htm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr" s="0">
+        <is>
+          <t>Mobile computing; cloud-based education; software architecture</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr" s="0">
+        <is>
+          <t>mobile computing; cloud education; software architecture</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1502/6727.htm</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr" s="0">
+        <is>
+          <t>Wang Tengjiao</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr" s="0">
+        <is>
+          <t>tjwang@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1500/6765.htm</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr" s="0">
+        <is>
+          <t>Database management system; web data management; big data management and mining</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr" s="0">
+        <is>
+          <t>database systems; web data; big data; data mining</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1500/6765.htm</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr" s="0">
+        <is>
+          <t>Wang Xiaolin</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr" s="0">
+        <is>
+          <t>wxl@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1500/6764.htm</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr" s="0">
+        <is>
+          <t>System virtualization; cloud computing</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr" s="0">
+        <is>
+          <t>virtualization; cloud computing; systems</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1500/6764.htm</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr" s="0">
+        <is>
+          <t>Xie Tao</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr" s="0">
+        <is>
+          <t>taoxie@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1502/9907.htm</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr" s="0">
+        <is>
+          <t>https://taoxiease.github.io/</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr" s="0">
+        <is>
+          <t>Software engineering; system software; software security</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr" s="0">
+        <is>
+          <t>software engineering; software security; testing</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1502/9907.htm</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; personal website listed on official page</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr" s="0">
+        <is>
+          <t>Zhang Ming</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr" s="0">
+        <is>
+          <t>mzhang_cs@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1500/6757.htm</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr" s="0">
+        <is>
+          <t>Machine learning; text mining</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr" s="0">
+        <is>
+          <t>machine learning; NLP; text mining; social network analysis</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1500/6757.htm</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="0">
+        <is>
+          <t>PKU-CS-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr" s="0">
+        <is>
+          <t>Peking University</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronics Engineering and Computer Science</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr" s="0">
+        <is>
+          <t>Zhang Wei</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr" s="0">
+        <is>
+          <t>zhangw.sei@pku.edu.cn</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1481/9872.htm</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr" s="0">
+        <is>
+          <t>Reuse-oriented requirements engineering; software development</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr" s="0">
+        <is>
+          <t>requirements engineering; software reuse; software development</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr" s="0">
+        <is>
+          <t>https://eecs.pku.edu.cn/xxkxjsxy/info/1481/9872.htm</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official PKU EECS faculty profile; Scholar and ResearchGate not yet verified</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/workbooks/professor_master.xlsx
+++ b/workbooks/professor_master.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Master</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T04:53:15Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T04:53:15Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -85,7 +85,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y13"/>
+  <dimension ref="A1:Y50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1739,6 +1739,4705 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t>THU-CS-001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr" s="0">
+        <is>
+          <t>Chen Weijun</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr" s="0">
+        <is>
+          <t>chenjw@tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1134/4146.htm</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr" s="0">
+        <is>
+          <t>Multimodal video understanding and generation</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr" s="0">
+        <is>
+          <t>multimodal video; generation; visual understanding</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1134/4146.htm</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tsinghua faculty profile</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr" s="0">
+        <is>
+          <t>THU-CS-002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr" s="0">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr" s="0">
+        <is>
+          <t>Xiang Yong</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr" s="0">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr" s="0">
+        <is>
+          <t>yx@tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1095/5774.htm</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr" s="0">
+        <is>
+          <t>Embodied artificial intelligence and multimodal content generation</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr" s="0">
+        <is>
+          <t>embodied AI; multimodal generation; machine learning</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1095/5774.htm</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tsinghua faculty profile</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr" s="0">
+        <is>
+          <t>THU-CS-003</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr" s="0">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr" s="0">
+        <is>
+          <t>Ma Yuchun</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr" s="0">
+        <is>
+          <t>mayc@tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1121/3975.htm</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr" s="0">
+        <is>
+          <t>Systems biology and knowledge engineering</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr" s="0">
+        <is>
+          <t>systems biology; knowledge engineering; AI for biology</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1121/3975.htm</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tsinghua faculty profile</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr" s="0">
+        <is>
+          <t>THU-CS-004</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr" s="0">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr" s="0">
+        <is>
+          <t>Qian Xuehai</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr" s="0">
+        <is>
+          <t>qxh-dcs@tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1091/3894.htm</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr" s="0">
+        <is>
+          <t>Computer architecture and chip design</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr" s="0">
+        <is>
+          <t>computer architecture; chips; systems</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1091/3894.htm</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tsinghua faculty profile</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="0">
+        <is>
+          <t>THU-CS-005</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr" s="0">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr" s="0">
+        <is>
+          <t>Yu Hongliang</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr" s="0">
+        <is>
+          <t>Assistant Professor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr" s="0">
+        <is>
+          <t>hongliangyu@tsinghua.edu.cn</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1147/5233.htm</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr" s="0">
+        <is>
+          <t>Networked systems and embodied AI</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr" s="0">
+        <is>
+          <t>networked systems; embodied AI; distributed systems</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.tsinghua.edu.cn/info/1147/5233.htm</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tsinghua faculty profile</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="0">
+        <is>
+          <t>FDU-CS-001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr" s="0">
+        <is>
+          <t>Fudan University</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr" s="0">
+        <is>
+          <t>Yang Chen</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr" s="0">
+        <is>
+          <t>chenyang@fudan.edu.cn</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.fudan.edu.cn/3f/c4/c24253a278468/page.htm</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr" s="0">
+        <is>
+          <t>Network measurement and mobile computing</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr" s="0">
+        <is>
+          <t>network measurement; mobile computing; networking</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.fudan.edu.cn/3f/c4/c24253a278468/page.htm</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Fudan faculty profile</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr" s="0">
+        <is>
+          <t>FDU-CS-002</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr" s="0">
+        <is>
+          <t>Fudan University</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr" s="0">
+        <is>
+          <t>Wu Yijian</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr" s="0">
+        <is>
+          <t>yjwu@fudan.edu.cn</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.fudan.edu.cn/3f/c8/c24253a278472/page.htm</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr" s="0">
+        <is>
+          <t>Computer system security</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr" s="0">
+        <is>
+          <t>system security; security; software and systems</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.fudan.edu.cn/3f/c8/c24253a278472/page.htm</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Fudan faculty profile</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="0">
+        <is>
+          <t>FDU-CS-003</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr" s="0">
+        <is>
+          <t>Fudan University</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr" s="0">
+        <is>
+          <t>Zhou Shuigeng</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr" s="0">
+        <is>
+          <t>sgzhou@fudan.edu.cn</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.fudan.edu.cn/43/04/c24253a279300/page.htm</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr" s="0">
+        <is>
+          <t>Database systems and data mining</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr" s="0">
+        <is>
+          <t>database systems; data mining; data management</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.fudan.edu.cn/43/04/c24253a279300/page.htm</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Fudan faculty profile</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="0">
+        <is>
+          <t>FDU-CS-004</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr" s="0">
+        <is>
+          <t>Fudan University</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr" s="0">
+        <is>
+          <t>Feng Rui</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr" s="0">
+        <is>
+          <t>fengrui@fudan.edu.cn</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.fudan.edu.cn/3f/bb/c24253a278459/page.htm</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr" s="0">
+        <is>
+          <t>Artificial intelligence</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr" s="0">
+        <is>
+          <t>artificial intelligence; machine learning</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.fudan.edu.cn/3f/bb/c24253a278459/page.htm</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Fudan faculty profile</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr" s="0">
+        <is>
+          <t>SJTU-CS-001</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr" s="0">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronic Information and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr" s="0">
+        <is>
+          <t>Chentao Wu</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr" s="0">
+        <is>
+          <t>chentao.wu@sjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=182</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr" s="0">
+        <is>
+          <t>Wireless networking and edge systems</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr" s="0">
+        <is>
+          <t>wireless networking; edge computing; systems</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=182</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official SJTU faculty profile</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr" s="0">
+        <is>
+          <t>SJTU-CS-002</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr" s="0">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronic Information and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr" s="0">
+        <is>
+          <t>Tu Shikui</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr" s="0">
+        <is>
+          <t>shtu@sjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=179</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr" s="0">
+        <is>
+          <t>Data science and intelligent computing</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr" s="0">
+        <is>
+          <t>data science; intelligent computing; data mining</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=179</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official SJTU faculty profile</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr" s="0">
+        <is>
+          <t>SJTU-CS-003</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr" s="0">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronic Information and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr" s="0">
+        <is>
+          <t>Gao Xiaofeng</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr" s="0">
+        <is>
+          <t>gaoxiaofeng@sjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=61</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr" s="0">
+        <is>
+          <t>Algorithms and optimization</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr" s="0">
+        <is>
+          <t>algorithms; optimization; networks</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=61</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official SJTU faculty profile</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr" s="0">
+        <is>
+          <t>SJTU-CS-004</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr" s="0">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronic Information and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr" s="0">
+        <is>
+          <t>Zheng Zhenzhe</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr" s="0">
+        <is>
+          <t>zhengzhenzhe@sjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=164</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr" s="0">
+        <is>
+          <t>Machine learning and computer vision</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr" s="0">
+        <is>
+          <t>machine learning; computer vision; AI</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=164</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official SJTU faculty profile</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr" s="0">
+        <is>
+          <t>SJTU-CS-005</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr" s="0">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr" s="0">
+        <is>
+          <t>School of Electronic Information and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr" s="0">
+        <is>
+          <t>Shen Yanyan</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr" s="0">
+        <is>
+          <t>shenyy@sjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=176</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr" s="0">
+        <is>
+          <t>Graph mining and data intelligence</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr" s="0">
+        <is>
+          <t>graph mining; data intelligence; data mining</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr" s="0">
+        <is>
+          <t>https://www.cs.sjtu.edu.cn/en/PeopleDetail.aspx?id=176</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official SJTU faculty profile</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr" s="0">
+        <is>
+          <t>ZJU-CS-001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr" s="0">
+        <is>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr" s="0">
+        <is>
+          <t>Xiao Jun</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr" s="0">
+        <is>
+          <t>junx@zju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/junx</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr" s="0">
+        <is>
+          <t>Multimedia analysis and intelligent interaction</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr" s="0">
+        <is>
+          <t>multimedia analysis; intelligent interaction; AI</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/junx</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Zhejiang University profile</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr" s="0">
+        <is>
+          <t>ZJU-CS-002</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr" s="0">
+        <is>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr" s="0">
+        <is>
+          <t>Qian Hui</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr" s="0">
+        <is>
+          <t>qianhui@zju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/qianhui</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr" s="0">
+        <is>
+          <t>Computer graphics and vision</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr" s="0">
+        <is>
+          <t>computer graphics; computer vision; visual computing</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/qianhui</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Zhejiang University profile</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr" s="0">
+        <is>
+          <t>ZJU-CS-003</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr" s="0">
+        <is>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr" s="0">
+        <is>
+          <t>Chen Lu</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr" s="0">
+        <is>
+          <t>luchen@zju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/luchen</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr" s="0">
+        <is>
+          <t>Database systems and knowledge engineering</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr" s="0">
+        <is>
+          <t>databases; knowledge engineering; data management</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/luchen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Zhejiang University profile</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr" s="0">
+        <is>
+          <t>ZJU-CS-004</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr" s="0">
+        <is>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr" s="0">
+        <is>
+          <t>Zheng Youyi</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr" s="0">
+        <is>
+          <t>yyzheng@zju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/yyzheng</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr" s="0">
+        <is>
+          <t>Computer vision and artificial intelligence</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr" s="0">
+        <is>
+          <t>computer vision; artificial intelligence; pattern recognition</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/yyzheng</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Zhejiang University profile</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr" s="0">
+        <is>
+          <t>ZJU-CS-005</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr" s="0">
+        <is>
+          <t>Zhejiang University</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr" s="0">
+        <is>
+          <t>Zhuang Yueting</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr" s="0">
+        <is>
+          <t>yzhuang@zju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/yzhuang</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr" s="0">
+        <is>
+          <t>Artificial intelligence and multimedia</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr" s="0">
+        <is>
+          <t>artificial intelligence; multimedia; pattern analysis</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr" s="0">
+        <is>
+          <t>https://person.zju.edu.cn/en/yzhuang</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Zhejiang University profile</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr" s="0">
+        <is>
+          <t>NJU-CS-001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr" s="0">
+        <is>
+          <t>Nanjing University</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr" s="0">
+        <is>
+          <t>Tong Lu</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr" s="0">
+        <is>
+          <t>lutong@nju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/tonglu/main.htm</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr" s="0">
+        <is>
+          <t>Human-computer interaction and ubiquitous computing</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr" s="0">
+        <is>
+          <t>HCI; ubiquitous computing; interactive systems</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/tonglu/main.htm</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Nanjing University profile</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr" s="0">
+        <is>
+          <t>NJU-CS-002</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr" s="0">
+        <is>
+          <t>Nanjing University</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr" s="0">
+        <is>
+          <t>Nie Changhai</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr" s="0">
+        <is>
+          <t>changhainie@nju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/changhai/main.htm</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr" s="0">
+        <is>
+          <t>Software testing and program analysis</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr" s="0">
+        <is>
+          <t>software testing; program analysis; software engineering</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/changhai/main.htm</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Nanjing University profile</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr" s="0">
+        <is>
+          <t>NJU-CS-003</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr" s="0">
+        <is>
+          <t>Nanjing University</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr" s="0">
+        <is>
+          <t>Bu Lei</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr" s="0">
+        <is>
+          <t>bulei@nju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/bulei/main.htm</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr" s="0">
+        <is>
+          <t>Cyber-physical systems and formal methods</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr" s="0">
+        <is>
+          <t>cyber-physical systems; formal methods; verification</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/bulei/main.htm</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Nanjing University profile</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr" s="0">
+        <is>
+          <t>NJU-CS-004</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr" s="0">
+        <is>
+          <t>Nanjing University</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr" s="0">
+        <is>
+          <t>Guo Yanwen</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr" s="0">
+        <is>
+          <t>guoyw@nju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/guoyw/main.htm</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr" s="0">
+        <is>
+          <t>Computer graphics and visual computing</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr" s="0">
+        <is>
+          <t>computer graphics; visual computing; rendering</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/guoyw/main.htm</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Nanjing University profile</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr" s="0">
+        <is>
+          <t>NJU-CS-005</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr" s="0">
+        <is>
+          <t>Nanjing University</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="0">
+        <is>
+          <t>Department of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr" s="0">
+        <is>
+          <t>Wu Jianxin</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr" s="0">
+        <is>
+          <t>wujx2001@nju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/wujx/main.htm</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr" s="0">
+        <is>
+          <t>Machine learning and pattern recognition</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr" s="0">
+        <is>
+          <t>machine learning; pattern recognition; computer vision</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.nju.edu.cn/wujx/main.htm</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Nanjing University profile</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr" s="0">
+        <is>
+          <t>USTC-CS-001</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr" s="0">
+        <is>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="0">
+        <is>
+          <t>Wang Shangfei</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr" s="0">
+        <is>
+          <t>wangsf@ustc.edu.cn</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/wangsf/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr" s="0">
+        <is>
+          <t>Affective computing and pattern recognition</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr" s="0">
+        <is>
+          <t>affective computing; pattern recognition; AI</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/wangsf/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official USTC faculty profile</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr" s="0">
+        <is>
+          <t>USTC-CS-002</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="0">
+        <is>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="0">
+        <is>
+          <t>Li Jing</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr" s="0">
+        <is>
+          <t>jingli@ustc.edu.cn</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/jingli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr" s="0">
+        <is>
+          <t>Multimedia computing and machine learning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr" s="0">
+        <is>
+          <t>multimedia computing; machine learning; AI</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/jingli/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official USTC faculty profile</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr" s="0">
+        <is>
+          <t>USTC-CS-003</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="0">
+        <is>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr" s="0">
+        <is>
+          <t>Li Xiangyang</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr" s="0">
+        <is>
+          <t>xiangyangli@ustc.edu.cn</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/lixy/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr" s="0">
+        <is>
+          <t>Algorithms and wireless networking</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr" s="0">
+        <is>
+          <t>algorithms; wireless networking; distributed systems</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/lixy/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official USTC faculty profile</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr" s="0">
+        <is>
+          <t>USTC-CS-004</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="0">
+        <is>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr" s="0">
+        <is>
+          <t>Liao Qianfang</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr" s="0">
+        <is>
+          <t>qfliao@ustc.edu.cn</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/qfliao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr" s="0">
+        <is>
+          <t>Computer vision and image processing</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr" s="0">
+        <is>
+          <t>computer vision; image processing; multimedia</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/qfliao/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official USTC faculty profile</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr" s="0">
+        <is>
+          <t>USTC-CS-005</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="0">
+        <is>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr" s="0">
+        <is>
+          <t>Shao Shuai</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr" s="0">
+        <is>
+          <t>sshuai@ustc.edu.cn</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/sshuai/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr" s="0">
+        <is>
+          <t>Computer systems and high-performance computing</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr" s="0">
+        <is>
+          <t>computer systems; HPC; architecture</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr" s="0">
+        <is>
+          <t>https://faculty.ustc.edu.cn/sshuai/zh_CN/index.htm</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official USTC faculty profile</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr" s="0">
+        <is>
+          <t>HIT-CS-001</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="0">
+        <is>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr" s="0">
+        <is>
+          <t>Shen Junqing</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.hit.edu.cn/2024/1128/c11271a362169/page.htm</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr" s="0">
+        <is>
+          <t>Computer architecture and storage systems</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr" s="0">
+        <is>
+          <t>computer architecture; storage systems; system software</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.hit.edu.cn/2024/1128/c11271a362169/page.htm</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HIT faculty profile; email not verified from public page</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr" s="0">
+        <is>
+          <t>HIT-CS-002</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="0">
+        <is>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr" s="0">
+        <is>
+          <t>Lv Xuan</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.hit.edu.cn/2024/1128/c11271a362174/page.htm</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr" s="0">
+        <is>
+          <t>Distributed computing and data systems</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr" s="0">
+        <is>
+          <t>distributed computing; data systems; systems</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.hit.edu.cn/2024/1128/c11271a362174/page.htm</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HIT faculty profile; email not verified from public page</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr" s="0">
+        <is>
+          <t>HIT-CS-003</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="0">
+        <is>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr" s="0">
+        <is>
+          <t>Li Quansheng</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.hit.edu.cn/2024/1128/c11271a362173/page.htm</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr" s="0">
+        <is>
+          <t>Artificial intelligence and computer vision</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr" s="0">
+        <is>
+          <t>artificial intelligence; computer vision; pattern recognition</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr" s="0">
+        <is>
+          <t>https://cs.hit.edu.cn/2024/1128/c11271a362173/page.htm</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HIT faculty profile; email not verified from public page</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr" s="0">
+        <is>
+          <t>XJTU-CS-001</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="0">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr" s="0">
+        <is>
+          <t>Xi Wei</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr" s="0">
+        <is>
+          <t>xw@mail.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/en/web/xiwei</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr" s="0">
+        <is>
+          <t>Computer vision and pattern recognition</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr" s="0">
+        <is>
+          <t>computer vision; pattern recognition; AI</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/en/web/xiwei</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Xi'an Jiaotong University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr" s="0">
+        <is>
+          <t>XJTU-CS-002</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="0">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr" s="0">
+        <is>
+          <t>Ding Han</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr" s="0">
+        <is>
+          <t>handing@mail.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/en/web/handing</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr" s="0">
+        <is>
+          <t>Human-computer interaction and intelligent design</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr" s="0">
+        <is>
+          <t>HCI; intelligent design; interactive computing</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/en/web/handing</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Xi'an Jiaotong University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr" s="0">
+        <is>
+          <t>XJTU-CS-003</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="0">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr" s="0">
+        <is>
+          <t>Tian Feng</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr" s="0">
+        <is>
+          <t>tianfeng@mail.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/en/web/fengtian</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr" s="0">
+        <is>
+          <t>Computer graphics and visual computing</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr" s="0">
+        <is>
+          <t>computer graphics; visual computing; rendering</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/en/web/fengtian</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Xi'an Jiaotong University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr" s="0">
+        <is>
+          <t>XJTU-CS-004</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="0">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr" s="0">
+        <is>
+          <t>Ren Xuebin</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr" s="0">
+        <is>
+          <t>renxuebin@mail.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/web/renxuebin</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr" s="0">
+        <is>
+          <t>Artificial intelligence and medical imaging</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr" s="0">
+        <is>
+          <t>artificial intelligence; medical imaging; image analysis</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/web/renxuebin</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Xi'an Jiaotong University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr" s="0">
+        <is>
+          <t>XJTU-CS-005</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="0">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr" s="0">
+        <is>
+          <t>Wang Wei</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr" s="0">
+        <is>
+          <t>wangw@mail.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/web/wwang</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr" s="0">
+        <is>
+          <t>Computer systems and software engineering</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr" s="0">
+        <is>
+          <t>computer systems; software engineering; systems</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr" s="0">
+        <is>
+          <t>https://gr.xjtu.edu.cn/web/wwang</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Xi'an Jiaotong University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/workbooks/professor_master.xlsx
+++ b/workbooks/professor_master.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Master</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:02:34Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:21Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:21Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 

--- a/workbooks/professor_master.xlsx
+++ b/workbooks/professor_master.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Master</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:08:21Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:08:21Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -85,7 +85,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6438,6 +6438,1530 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr" s="0">
+        <is>
+          <t>XJTU-THERMO-001</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr" s="0">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="0">
+        <is>
+          <t>Engineering Thermophysics</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr" s="0">
+        <is>
+          <t>CHENG Zedong</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr" s="0">
+        <is>
+          <t>zedongchneg@mail.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr" s="0">
+        <is>
+          <t>renewable energy; solar thermochemical fuels; energy storage; desalination</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr" s="0">
+        <is>
+          <t>renewable energy; solar thermochemical fuels; energy storage; desalination</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook XJTU_Selected_Professors.xlsx; user-curated professor list</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr" s="0">
+        <is>
+          <t>XJTU-THERMO-002</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr" s="0">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="0">
+        <is>
+          <t>Engineering Thermophysics</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr" s="0">
+        <is>
+          <t>LI Yinshi</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr" s="0">
+        <is>
+          <t>ysli@mail.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr" s="0">
+        <is>
+          <t>fuel cells; flow batteries; renewable energy storage</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr" s="0">
+        <is>
+          <t>fuel cells; flow batteries; renewable energy storage</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook XJTU_Selected_Professors.xlsx; user-curated professor list</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr" s="0">
+        <is>
+          <t>XJTU-THERMO-003</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr" s="0">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="0">
+        <is>
+          <t>Engineering Thermophysics</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr" s="0">
+        <is>
+          <t>YANG Weiwei</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr" s="0">
+        <is>
+          <t>yangww@mail.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr" s="0">
+        <is>
+          <t>fuel cells; energy storage; renewable energy</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr" s="0">
+        <is>
+          <t>fuel cells; energy storage; renewable energy</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook XJTU_Selected_Professors.xlsx; user-curated professor list</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr" s="0">
+        <is>
+          <t>NCEPU-001</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr" s="0">
+        <is>
+          <t>North China Electric Power University</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr" s="0">
+        <is>
+          <t>211_only</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="0">
+        <is>
+          <t>School of Energy</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr" s="0">
+        <is>
+          <t>Power and Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr" s="0">
+        <is>
+          <t>Wei Gaosheng</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr" s="0">
+        <is>
+          <t>gaoshengw@126.com</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr" s="0">
+        <is>
+          <t>solar thermal power generation; thermal energy storage; micro and nano-scale heat transfer</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr" s="0">
+        <is>
+          <t>solar thermal power; thermal energy storage; micro heat transfer</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr" s="0">
+        <is>
+          <t>NCEPU-002</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr" s="0">
+        <is>
+          <t>North China Electric Power University</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr" s="0">
+        <is>
+          <t>211_only</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="0">
+        <is>
+          <t>School of Energy</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr" s="0">
+        <is>
+          <t>Power and Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr" s="0">
+        <is>
+          <t>Yang Xueming</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr" s="0">
+        <is>
+          <t>micro and nano-scale heat and mass transfer; clean energy utilization; energy storage thermophysics</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr" s="0">
+        <is>
+          <t>micro heat transfer; clean energy; energy storage thermophysics</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list; email missing in source row preview</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr" s="0">
+        <is>
+          <t>NCEPU-003</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr" s="0">
+        <is>
+          <t>North China Electric Power University</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr" s="0">
+        <is>
+          <t>211_only</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="0">
+        <is>
+          <t>School of Energy</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr" s="0">
+        <is>
+          <t>Power and Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr" s="0">
+        <is>
+          <t>Zhang Yuning</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr" s="0">
+        <is>
+          <t>high-speed flow; cavitation; multiphase flow; clean energy fluid dynamics</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr" s="0">
+        <is>
+          <t>high-speed flow; cavitation; multiphase flow; fluid dynamics</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list; email missing in source row preview</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr" s="0">
+        <is>
+          <t>SZU-001</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr" s="0">
+        <is>
+          <t>Shenzhen University</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr" s="0">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="0">
+        <is>
+          <t>School of Architecture and Urban Planning</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr" s="0">
+        <is>
+          <t>Huang Zhengdong</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr" s="0">
+        <is>
+          <t>huangwhu@126.com</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr" s="0">
+        <is>
+          <t>Urban Planning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr" s="0">
+        <is>
+          <t>urban planning</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook Shenzhen University.xlsx; user-curated professor list</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr" s="0">
+        <is>
+          <t>SZU-002</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr" s="0">
+        <is>
+          <t>Shenzhen University</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr" s="0">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="0">
+        <is>
+          <t>School of Architecture and Urban Planning</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr" s="0">
+        <is>
+          <t>Chisheng Wang</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr" s="0">
+        <is>
+          <t>wangchisheng@szu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr" s="0">
+        <is>
+          <t>remote sensing image processing and smart city development</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr" s="0">
+        <is>
+          <t>remote sensing; image processing; smart city</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr" s="0">
+        <is>
+          <t>Contacted</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook Shenzhen University.xlsx; progress noted as 1st Email Done</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr" s="0">
+        <is>
+          <t>SZU-003</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr" s="0">
+        <is>
+          <t>Shenzhen University</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr" s="0">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="0">
+        <is>
+          <t>College of Computer Science and Software Engineering</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr" s="0">
+        <is>
+          <t>Victor Chung Ming Leung</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr" s="0">
+        <is>
+          <t>vleung@ieee.org</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr" s="0">
+        <is>
+          <t>mobile computing; intelligent networking; artificial intelligence</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr" s="0">
+        <is>
+          <t>mobile computing; intelligent networking; artificial intelligence</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook Shenzhen University.xlsx; user-curated professor list</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr" s="0">
+        <is>
+          <t>HITSZ-001</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr" s="0">
+        <is>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="0">
+        <is>
+          <t>School of Energy Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr" s="0">
+        <is>
+          <t>HIT Shenzhen</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr" s="0">
+        <is>
+          <t>Shuai Yong</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr" s="0">
+        <is>
+          <t>shuaiyong@hit.edu.cn</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr" s="0">
+        <is>
+          <t>Contacted</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen; progress noted as 1st email</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr" s="0">
+        <is>
+          <t>HITSZ-002</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr" s="0">
+        <is>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="0">
+        <is>
+          <t>School of Energy Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr" s="0">
+        <is>
+          <t>HIT Shenzhen</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr" s="0">
+        <is>
+          <t>Yu Daren</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr" s="0">
+        <is>
+          <t>yudaren@hit.edu.cn</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr" s="0">
+        <is>
+          <t>HITSZ-003</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr" s="0">
+        <is>
+          <t>Harbin Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr" s="0">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="0">
+        <is>
+          <t>School of Energy Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr" s="0">
+        <is>
+          <t>HIT Shenzhen</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr" s="0">
+        <is>
+          <t>Liu Jinfu</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr" s="0">
+        <is>
+          <t>jinfuliu@hit.edu.cn</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr" s="0">
+        <is>
+          <t>modeling; control; early warning; diagnosis; intelligent maintenance of power systems; new energy; energy internet; integrated smart energy</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr" s="0">
+        <is>
+          <t>modeling; control; diagnosis; smart maintenance; new energy; energy internet</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr" s="0">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr" s="0">
+        <is>
+          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/workbooks/professor_master.xlsx
+++ b/workbooks/professor_master.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Master</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:17:49Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:43Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:43Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -85,7 +85,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y62"/>
+  <dimension ref="A1:Y74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7962,6 +7962,1530 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr" s="0">
+        <is>
+          <t>WHU-CS-001</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr" s="0">
+        <is>
+          <t>Wuhan University</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr" s="0">
+        <is>
+          <t>Sheng Wang</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr" s="0">
+        <is>
+          <t>https://sheng.whu.edu.cn/</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr" s="0">
+        <is>
+          <t>Multi-model database theory and systems</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr" s="0">
+        <is>
+          <t>multi-model databases; systems; data markets; scientific discovery</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr" s="0">
+        <is>
+          <t>https://sheng.whu.edu.cn/</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official WHU personal page on whu.edu.cn domain</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr" s="0">
+        <is>
+          <t>WHU-CS-002</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr" s="0">
+        <is>
+          <t>Wuhan University</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr" s="0">
+        <is>
+          <t>Hao Wang</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr" s="0">
+        <is>
+          <t>wanghao.cs@whu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr" s="0">
+        <is>
+          <t>https://jszy.whu.edu.cn/wanghao6/en/index.htm</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr" s="0">
+        <is>
+          <t>spatiotemporal data management; interactive learning; recommender systems</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr" s="0">
+        <is>
+          <t>spatiotemporal data; interactive learning; recommender systems</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr" s="0">
+        <is>
+          <t>https://jszy.whu.edu.cn/wanghao6/en/index.htm</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Wuhan University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr" s="0">
+        <is>
+          <t>HUST-CS-001</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="0">
+        <is>
+          <t>Jin Renchao</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr" s="0">
+        <is>
+          <t>jrc@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1446/1433.htm</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr" s="0">
+        <is>
+          <t>Artificial intelligence; medical image processing and analysis; computer vision</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr" s="0">
+        <is>
+          <t>artificial intelligence; medical image analysis; computer vision</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1446/1433.htm</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HUST faculty profile</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr" s="0">
+        <is>
+          <t>HUST-CS-002</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr" s="0">
+        <is>
+          <t>Chen Jincai</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr" s="0">
+        <is>
+          <t>jcchen@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1464/1187.htm</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr" s="0">
+        <is>
+          <t>New memory theory and technology; big data storage and analysis; machine learning; image processing</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr" s="0">
+        <is>
+          <t>new memory; big data; machine learning; image processing</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1464/1187.htm</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HUST faculty profile</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr" s="0">
+        <is>
+          <t>HUST-CS-003</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr" s="0">
+        <is>
+          <t>Hu Long</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr" s="0">
+        <is>
+          <t>hulong@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1724/1427.htm</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr" s="0">
+        <is>
+          <t>Emotional computing; edge computing; software defined network; big data</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr" s="0">
+        <is>
+          <t>emotional computing; edge computing; SDN; big data</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1724/1427.htm</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HUST faculty profile</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr" s="0">
+        <is>
+          <t>HUST-CS-004</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr" s="0">
+        <is>
+          <t>Wei Wei</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr" s="0">
+        <is>
+          <t>weiw@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1553/1661.htm</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr" s="0">
+        <is>
+          <t>Artificial intelligence; natural language processing; information retrieval; textual data mining; recommendation systems; deep learning</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr" s="0">
+        <is>
+          <t>artificial intelligence; NLP; IR; data mining; recommender systems; deep learning</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1553/1661.htm</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HUST faculty profile</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr" s="0">
+        <is>
+          <t>HUST-CS-005</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr" s="0">
+        <is>
+          <t>Gu Lin</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr" s="0">
+        <is>
+          <t>lingu@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1319/1196.htm</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr" s="0">
+        <is>
+          <t>Cloud native; serverless computing; microservice; edge computing</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr" s="0">
+        <is>
+          <t>cloud native; serverless; microservices; edge computing</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1319/1196.htm</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HUST faculty profile</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr" s="0">
+        <is>
+          <t>TJU-CS-001</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr" s="0">
+        <is>
+          <t>Bo Wang</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr" s="0">
+        <is>
+          <t>B_o_wang@tju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr" s="0">
+        <is>
+          <t>https://tiei.tju.edu.cn/info/1614/3494.htm</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr" s="0">
+        <is>
+          <t>http://cs.tju.edu.cn/faculty/wangbo/index.htm</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr" s="0">
+        <is>
+          <t>Intelligent dialog systems; computational psychology; personalized recommendation; natural language processing</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr" s="0">
+        <is>
+          <t>intelligent dialog; computational psychology; recommendation; NLP</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr" s="0">
+        <is>
+          <t>https://tiei.tju.edu.cn/info/1614/3494.htm</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tianjin University profile</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr" s="0">
+        <is>
+          <t>TJU-CS-002</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr" s="0">
+        <is>
+          <t>Kun Li</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr" s="0">
+        <is>
+          <t>lik@tju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/likun/bio.html</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr" s="0">
+        <is>
+          <t>3D vision and digital humans</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr" s="0">
+        <is>
+          <t>3D vision; digital humans; computer vision</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/likun/bio.html</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tianjin University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr" s="0">
+        <is>
+          <t>TJU-CS-003</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr" s="0">
+        <is>
+          <t>Guangquan Xu</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr" s="0">
+        <is>
+          <t>losin@tju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/xugq/index.htm</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr" s="0">
+        <is>
+          <t>Network security and intelligent monitoring</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr" s="0">
+        <is>
+          <t>network security; intelligent monitoring; software engineering</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/xugq/index.htm</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tianjin University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr" s="0">
+        <is>
+          <t>TONGJI-001</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr" s="0">
+        <is>
+          <t>Tongji University</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="0">
+        <is>
+          <t>Department of Control Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr" s="0">
+        <is>
+          <t>College of Electronic and Information Engineering</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr" s="0">
+        <is>
+          <t>Shi Miaojing</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr" s="0">
+        <is>
+          <t>mshi@tongji.edu.cn</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr" s="0">
+        <is>
+          <t>https://see-en.tongji.edu.cn/info/1016/1522.htm</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr" s="0">
+        <is>
+          <t>https://sites.google.com/site/miaojingshi/</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr" s="0">
+        <is>
+          <t>Computer vision; machine learning; multimedia computing</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr" s="0">
+        <is>
+          <t>computer vision; machine learning; multimedia computing</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr" s="0">
+        <is>
+          <t>https://see-en.tongji.edu.cn/info/1016/1522.htm</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tongji faculty profile</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr" s="0">
+        <is>
+          <t>SYSU-001</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="0">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="0">
+        <is>
+          <t>Li Wenjun</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr" s="0">
+        <is>
+          <t>lnslwj@mail.sysu.edu.cn</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr" s="0">
+        <is>
+          <t>https://cse.sysu.edu.cn/en/teacher/LiWenjun</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr" s="0">
+        <is>
+          <t>Computer science and software systems</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr" s="0">
+        <is>
+          <t>computer science; software systems</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr" s="0">
+        <is>
+          <t>https://cse.sysu.edu.cn/en/teacher/LiWenjun</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official SYSU faculty profile</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/workbooks/professor_master.xlsx
+++ b/workbooks/professor_master.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Master</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:30:43Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:30:43Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
@@ -85,7 +85,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6822,47 +6822,47 @@
     <row r="54">
       <c r="A54" t="inlineStr" s="0">
         <is>
-          <t>NCEPU-001</t>
+          <t>XJTU-THERMO-004</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="0">
         <is>
-          <t>North China Electric Power University</t>
+          <t>Xi'an Jiaotong University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="0">
         <is>
-          <t>211_only</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="0">
         <is>
-          <t>School of Energy</t>
+          <t>Engineering Thermophysics</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="0">
         <is>
-          <t>Power and Mechanical Engineering</t>
+          <t/>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Tao Yubing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr" s="0">
         <is>
-          <t>Wei Gaosheng</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr" s="0">
         <is>
-          <t>Professor</t>
+          <t>yubingtao@xjtu.edu.cn</t>
         </is>
       </c>
       <c r="I54" t="inlineStr" s="0">
         <is>
-          <t>gaoshengw@126.com</t>
+          <t/>
         </is>
       </c>
       <c r="J54" t="inlineStr" s="0">
@@ -6872,17 +6872,17 @@
       </c>
       <c r="K54" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>thermal energy storage; enhanced heat and mass transfer</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="0">
         <is>
-          <t>solar thermal power generation; thermal energy storage; micro and nano-scale heat transfer</t>
+          <t>thermal energy storage; heat transfer; mass transfer</t>
         </is>
       </c>
       <c r="M54" t="inlineStr" s="0">
         <is>
-          <t>solar thermal power; thermal energy storage; micro heat transfer</t>
+          <t/>
         </is>
       </c>
       <c r="N54" t="inlineStr" s="0">
@@ -6897,94 +6897,94 @@
       </c>
       <c r="P54" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr" s="0">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R54" t="inlineStr" s="0">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S54" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>Not contacted</t>
         </is>
       </c>
       <c r="T54" t="inlineStr" s="0">
         <is>
-          <t>Not contacted</t>
+          <t/>
         </is>
       </c>
       <c r="U54" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>No response</t>
         </is>
       </c>
       <c r="V54" t="inlineStr" s="0">
         <is>
-          <t>No response</t>
+          <t/>
         </is>
       </c>
       <c r="W54" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="X54" t="inlineStr" s="0">
         <is>
-          <t>2026-03-14</t>
+          <t>Imported from local workbook XJTU_Selected_Professors_With_Ranking.xlsx; user-curated professor list</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr" s="0">
         <is>
-          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr" s="0">
         <is>
-          <t>NCEPU-002</t>
+          <t>XJTU-THERMO-005</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="0">
         <is>
-          <t>North China Electric Power University</t>
+          <t>Xi'an Jiaotong University</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="0">
         <is>
-          <t>211_only</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="0">
         <is>
-          <t>School of Energy</t>
+          <t>Engineering Thermophysics</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="0">
         <is>
-          <t>Power and Mechanical Engineering</t>
+          <t/>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>HE Yaling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr" s="0">
         <is>
-          <t>Yang Xueming</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr" s="0">
         <is>
-          <t>Professor</t>
+          <t>yalinghe@mail.xjtu.edu.cn</t>
         </is>
       </c>
       <c r="I55" t="inlineStr" s="0">
@@ -6999,17 +6999,17 @@
       </c>
       <c r="K55" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>renewable energy; fuel cells; heat transfer</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="0">
         <is>
-          <t>micro and nano-scale heat and mass transfer; clean energy utilization; energy storage thermophysics</t>
+          <t>renewable energy; fuel cells; heat transfer</t>
         </is>
       </c>
       <c r="M55" t="inlineStr" s="0">
         <is>
-          <t>micro heat transfer; clean energy; energy storage thermophysics</t>
+          <t/>
         </is>
       </c>
       <c r="N55" t="inlineStr" s="0">
@@ -7024,94 +7024,94 @@
       </c>
       <c r="P55" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr" s="0">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R55" t="inlineStr" s="0">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S55" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>Not contacted</t>
         </is>
       </c>
       <c r="T55" t="inlineStr" s="0">
         <is>
-          <t>Not contacted</t>
+          <t/>
         </is>
       </c>
       <c r="U55" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>No response</t>
         </is>
       </c>
       <c r="V55" t="inlineStr" s="0">
         <is>
-          <t>No response</t>
+          <t/>
         </is>
       </c>
       <c r="W55" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="X55" t="inlineStr" s="0">
         <is>
-          <t>2026-03-14</t>
+          <t>Imported from local workbook XJTU_Selected_Professors_With_Ranking.xlsx; user-curated professor list</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr" s="0">
         <is>
-          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list; email missing in source row preview</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr" s="0">
         <is>
-          <t>NCEPU-003</t>
+          <t>XJTU-THERMO-006</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="0">
         <is>
-          <t>North China Electric Power University</t>
+          <t>Xi'an Jiaotong University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="0">
         <is>
-          <t>211_only</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="0">
         <is>
-          <t>School of Energy</t>
+          <t>Engineering Thermophysics</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="0">
         <is>
-          <t>Power and Mechanical Engineering</t>
+          <t/>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>WANG Qiuwang</t>
         </is>
       </c>
       <c r="G56" t="inlineStr" s="0">
         <is>
-          <t>Zhang Yuning</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr" s="0">
         <is>
-          <t>Professor</t>
+          <t>wangqw@mail.xjtu.edu.cn</t>
         </is>
       </c>
       <c r="I56" t="inlineStr" s="0">
@@ -7126,17 +7126,17 @@
       </c>
       <c r="K56" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>prediction and optimization; high-efficiency heat exchangers</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="0">
         <is>
-          <t>high-speed flow; cavitation; multiphase flow; clean energy fluid dynamics</t>
+          <t>prediction; optimization; heat exchangers</t>
         </is>
       </c>
       <c r="M56" t="inlineStr" s="0">
         <is>
-          <t>high-speed flow; cavitation; multiphase flow; fluid dynamics</t>
+          <t/>
         </is>
       </c>
       <c r="N56" t="inlineStr" s="0">
@@ -7151,74 +7151,74 @@
       </c>
       <c r="P56" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr" s="0">
         <is>
-          <t>Unknown</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R56" t="inlineStr" s="0">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S56" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>Not contacted</t>
         </is>
       </c>
       <c r="T56" t="inlineStr" s="0">
         <is>
-          <t>Not contacted</t>
+          <t/>
         </is>
       </c>
       <c r="U56" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>No response</t>
         </is>
       </c>
       <c r="V56" t="inlineStr" s="0">
         <is>
-          <t>No response</t>
+          <t/>
         </is>
       </c>
       <c r="W56" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="X56" t="inlineStr" s="0">
         <is>
-          <t>2026-03-14</t>
+          <t>Imported from local workbook XJTU_Selected_Professors_With_Ranking.xlsx; user-curated professor list</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr" s="0">
         <is>
-          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list; email missing in source row preview</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr" s="0">
         <is>
-          <t>SZU-001</t>
+          <t>XJTU-THERMO-007</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="0">
         <is>
-          <t>Shenzhen University</t>
+          <t>Xi'an Jiaotong University</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="0">
         <is>
-          <t>other</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="0">
         <is>
-          <t>School of Architecture and Urban Planning</t>
+          <t>Thermal Energy and Power</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="0">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F57" t="inlineStr" s="0">
         <is>
-          <t>Huang Zhengdong</t>
+          <t>SHI Jinwen</t>
         </is>
       </c>
       <c r="G57" t="inlineStr" s="0">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="H57" t="inlineStr" s="0">
         <is>
-          <t>huangwhu@126.com</t>
+          <t>Jinwen_shi@mail.xjtu.edu.cn</t>
         </is>
       </c>
       <c r="I57" t="inlineStr" s="0">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="K57" t="inlineStr" s="0">
         <is>
-          <t>Urban Planning</t>
+          <t>solar energy; hydrogen; photocatalysis</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="0">
         <is>
-          <t>urban planning</t>
+          <t>solar energy; hydrogen; photocatalysis</t>
         </is>
       </c>
       <c r="M57" t="inlineStr" s="0">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="X57" t="inlineStr" s="0">
         <is>
-          <t>Imported from local workbook Shenzhen University.xlsx; user-curated professor list</t>
+          <t>Imported from local workbook XJTU_Selected_Professors_With_Ranking.xlsx; user-curated professor list</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr" s="0">
@@ -7330,47 +7330,47 @@
     <row r="58">
       <c r="A58" t="inlineStr" s="0">
         <is>
-          <t>SZU-002</t>
+          <t>NCEPU-001</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="0">
         <is>
-          <t>Shenzhen University</t>
+          <t>North China Electric Power University</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="0">
         <is>
-          <t>other</t>
+          <t>211_only</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="0">
         <is>
-          <t>School of Architecture and Urban Planning</t>
+          <t>School of Energy</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Power and Mechanical Engineering</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="0">
         <is>
-          <t>Chisheng Wang</t>
+          <t/>
         </is>
       </c>
       <c r="G58" t="inlineStr" s="0">
         <is>
+          <t>Wei Gaosheng</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr" s="0">
+        <is>
           <t>Professor</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr" s="0">
-        <is>
-          <t>wangchisheng@szu.edu.cn</t>
-        </is>
-      </c>
       <c r="I58" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>gaoshengw@126.com</t>
         </is>
       </c>
       <c r="J58" t="inlineStr" s="0">
@@ -7380,17 +7380,17 @@
       </c>
       <c r="K58" t="inlineStr" s="0">
         <is>
-          <t>remote sensing image processing and smart city development</t>
+          <t/>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="0">
         <is>
-          <t>remote sensing; image processing; smart city</t>
+          <t>solar thermal power generation; thermal energy storage; micro and nano-scale heat transfer</t>
         </is>
       </c>
       <c r="M58" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>solar thermal power; thermal energy storage; micro heat transfer</t>
         </is>
       </c>
       <c r="N58" t="inlineStr" s="0">
@@ -7405,96 +7405,96 @@
       </c>
       <c r="P58" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr" s="0">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr" s="0">
+      <c r="R58" t="inlineStr" s="0">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr" s="0">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="S58" t="inlineStr" s="0">
         <is>
-          <t>Contacted</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T58" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Not contacted</t>
         </is>
       </c>
       <c r="U58" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr" s="0">
+        <is>
           <t>No response</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="W58" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr" s="0">
+        <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr" s="0">
-        <is>
-          <t>Imported from local workbook Shenzhen University.xlsx; progress noted as 1st Email Done</t>
-        </is>
-      </c>
       <c r="Y58" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr" s="0">
         <is>
-          <t>SZU-003</t>
+          <t>NCEPU-002</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="0">
         <is>
-          <t>Shenzhen University</t>
+          <t>North China Electric Power University</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="0">
         <is>
-          <t>other</t>
+          <t>211_only</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="0">
         <is>
-          <t>College of Computer Science and Software Engineering</t>
+          <t>School of Energy</t>
         </is>
       </c>
       <c r="E59" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Power and Mechanical Engineering</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="0">
         <is>
-          <t>Victor Chung Ming Leung</t>
+          <t/>
         </is>
       </c>
       <c r="G59" t="inlineStr" s="0">
         <is>
+          <t>Yang Xueming</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr" s="0">
+        <is>
           <t>Professor</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr" s="0">
-        <is>
-          <t>vleung@ieee.org</t>
-        </is>
-      </c>
       <c r="I59" t="inlineStr" s="0">
         <is>
           <t/>
@@ -7507,17 +7507,17 @@
       </c>
       <c r="K59" t="inlineStr" s="0">
         <is>
-          <t>mobile computing; intelligent networking; artificial intelligence</t>
+          <t/>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="0">
         <is>
-          <t>mobile computing; intelligent networking; artificial intelligence</t>
+          <t>micro and nano-scale heat and mass transfer; clean energy utilization; energy storage thermophysics</t>
         </is>
       </c>
       <c r="M59" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>micro heat transfer; clean energy; energy storage thermophysics</t>
         </is>
       </c>
       <c r="N59" t="inlineStr" s="0">
@@ -7532,96 +7532,96 @@
       </c>
       <c r="P59" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr" s="0">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr" s="0">
+      <c r="R59" t="inlineStr" s="0">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr" s="0">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="S59" t="inlineStr" s="0">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr" s="0">
+        <is>
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U59" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr" s="0">
+        <is>
           <t>No response</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="W59" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr" s="0">
+        <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr" s="0">
-        <is>
-          <t>Imported from local workbook Shenzhen University.xlsx; user-curated professor list</t>
-        </is>
-      </c>
       <c r="Y59" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list; email missing in source row preview</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr" s="0">
         <is>
-          <t>HITSZ-001</t>
+          <t>NCEPU-003</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="0">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>North China Electric Power University</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="0">
         <is>
-          <t>C9</t>
+          <t>211_only</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="0">
         <is>
-          <t>School of Energy Science and Engineering</t>
+          <t>School of Energy</t>
         </is>
       </c>
       <c r="E60" t="inlineStr" s="0">
         <is>
-          <t>HIT Shenzhen</t>
+          <t>Power and Mechanical Engineering</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="0">
         <is>
-          <t>Shuai Yong</t>
+          <t/>
         </is>
       </c>
       <c r="G60" t="inlineStr" s="0">
         <is>
+          <t>Zhang Yuning</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr" s="0">
+        <is>
           <t>Professor</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr" s="0">
-        <is>
-          <t>shuaiyong@hit.edu.cn</t>
-        </is>
-      </c>
       <c r="I60" t="inlineStr" s="0">
         <is>
           <t/>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="L60" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>high-speed flow; cavitation; multiphase flow; clean energy fluid dynamics</t>
         </is>
       </c>
       <c r="M60" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>high-speed flow; cavitation; multiphase flow; fluid dynamics</t>
         </is>
       </c>
       <c r="N60" t="inlineStr" s="0">
@@ -7659,99 +7659,99 @@
       </c>
       <c r="P60" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr" s="0">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr" s="0">
+      <c r="R60" t="inlineStr" s="0">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr" s="0">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="S60" t="inlineStr" s="0">
         <is>
-          <t>Contacted</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="T60" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Not contacted</t>
         </is>
       </c>
       <c r="U60" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr" s="0">
+        <is>
           <t>No response</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="W60" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr" s="0">
+        <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr" s="0">
-        <is>
-          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen; progress noted as 1st email</t>
-        </is>
-      </c>
       <c r="Y60" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list; email missing in source row preview</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr" s="0">
         <is>
-          <t>HITSZ-002</t>
+          <t>NCEPU-004</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="0">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>North China Electric Power University</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="0">
         <is>
-          <t>C9</t>
+          <t>211_only</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="0">
         <is>
-          <t>School of Energy Science and Engineering</t>
+          <t>School of Energy</t>
         </is>
       </c>
       <c r="E61" t="inlineStr" s="0">
         <is>
-          <t>HIT Shenzhen</t>
+          <t>Power and Mechanical Engineering</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="0">
         <is>
-          <t>Yu Daren</t>
+          <t/>
         </is>
       </c>
       <c r="G61" t="inlineStr" s="0">
         <is>
+          <t>Wang Zhangqi</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr" s="0">
+        <is>
           <t>Professor</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr" s="0">
-        <is>
-          <t>yudaren@hit.edu.cn</t>
-        </is>
-      </c>
       <c r="I61" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>wangzq2093@163.com</t>
         </is>
       </c>
       <c r="J61" t="inlineStr" s="0">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="L61" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>transmission line engineering; wind power equipment; structural dynamics and reliability</t>
         </is>
       </c>
       <c r="M61" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>transmission line engineering; wind power; structural dynamics; reliability</t>
         </is>
       </c>
       <c r="N61" t="inlineStr" s="0">
@@ -7786,96 +7786,96 @@
       </c>
       <c r="P61" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr" s="0">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr" s="0">
+      <c r="R61" t="inlineStr" s="0">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr" s="0">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="S61" t="inlineStr" s="0">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr" s="0">
+        <is>
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U61" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr" s="0">
+        <is>
           <t>No response</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="W61" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr" s="0">
+        <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr" s="0">
-        <is>
-          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen</t>
-        </is>
-      </c>
       <c r="Y61" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr" s="0">
         <is>
-          <t>HITSZ-003</t>
+          <t>NCEPU-005</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="0">
         <is>
-          <t>Harbin Institute of Technology</t>
+          <t>North China Electric Power University</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="0">
         <is>
-          <t>C9</t>
+          <t>211_only</t>
         </is>
       </c>
       <c r="D62" t="inlineStr" s="0">
         <is>
-          <t>School of Energy Science and Engineering</t>
+          <t>School of Energy</t>
         </is>
       </c>
       <c r="E62" t="inlineStr" s="0">
         <is>
-          <t>HIT Shenzhen</t>
+          <t>Power and Mechanical Engineering</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="0">
         <is>
-          <t>Liu Jinfu</t>
+          <t/>
         </is>
       </c>
       <c r="G62" t="inlineStr" s="0">
         <is>
+          <t>Yang Lijun</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr" s="0">
+        <is>
           <t>Professor</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr" s="0">
-        <is>
-          <t>jinfuliu@hit.edu.cn</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr" s="0">
         <is>
           <t/>
@@ -7888,17 +7888,17 @@
       </c>
       <c r="K62" t="inlineStr" s="0">
         <is>
-          <t>modeling; control; early warning; diagnosis; intelligent maintenance of power systems; new energy; energy internet; integrated smart energy</t>
+          <t/>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="0">
         <is>
-          <t>modeling; control; diagnosis; smart maintenance; new energy; energy internet</t>
+          <t>electrochemical energy storage; hydrogen energy; power plant flexibility; CO2 reduction</t>
         </is>
       </c>
       <c r="M62" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>electrochemical storage; hydrogen; power plant flexibility; CO2 reduction</t>
         </is>
       </c>
       <c r="N62" t="inlineStr" s="0">
@@ -7913,84 +7913,84 @@
       </c>
       <c r="P62" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr" s="0">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr" s="0">
+      <c r="R62" t="inlineStr" s="0">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr" s="0">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="S62" t="inlineStr" s="0">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr" s="0">
+        <is>
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="U62" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr" s="0">
+        <is>
           <t>No response</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="W62" t="inlineStr" s="0">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr" s="0">
+        <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr" s="0">
-        <is>
-          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen</t>
-        </is>
-      </c>
       <c r="Y62" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>Imported from local workbook NCEPU_Professors_PhD_Emails_All.xlsx; user-curated professor list; email missing in source row preview</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr" s="0">
         <is>
-          <t>WHU-CS-001</t>
+          <t>SZU-001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="0">
         <is>
-          <t>Wuhan University</t>
+          <t>Shenzhen University</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="0">
         <is>
-          <t>985_non_C9</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science</t>
+          <t>School of Architecture and Urban Planning</t>
         </is>
       </c>
       <c r="E63" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science</t>
+          <t/>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="0">
         <is>
-          <t>Sheng Wang</t>
+          <t>Huang Zhengdong</t>
         </is>
       </c>
       <c r="G63" t="inlineStr" s="0">
@@ -8000,12 +8000,12 @@
       </c>
       <c r="H63" t="inlineStr" s="0">
         <is>
-          <t/>
+          <t>huangwhu@126.com</t>
         </is>
       </c>
       <c r="I63" t="inlineStr" s="0">
         <is>
-          <t>https://sheng.whu.edu.cn/</t>
+          <t/>
         </is>
       </c>
       <c r="J63" t="inlineStr" s="0">
@@ -8015,12 +8015,12 @@
       </c>
       <c r="K63" t="inlineStr" s="0">
         <is>
-          <t>Multi-model database theory and systems</t>
+          <t>Urban Planning</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="0">
         <is>
-          <t>multi-model databases; systems; data markets; scientific discovery</t>
+          <t>urban planning</t>
         </is>
       </c>
       <c r="M63" t="inlineStr" s="0">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="P63" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R63" t="inlineStr" s="0">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="V63" t="inlineStr" s="0">
         <is>
-          <t>https://sheng.whu.edu.cn/</t>
+          <t/>
         </is>
       </c>
       <c r="W63" t="inlineStr" s="0">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="X63" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official WHU personal page on whu.edu.cn domain</t>
+          <t>Imported from local workbook Shenzhen University.xlsx; user-curated professor list</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr" s="0">
@@ -8092,32 +8092,32 @@
     <row r="64">
       <c r="A64" t="inlineStr" s="0">
         <is>
-          <t>WHU-CS-002</t>
+          <t>SZU-002</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="0">
         <is>
-          <t>Wuhan University</t>
+          <t>Shenzhen University</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="0">
         <is>
-          <t>985_non_C9</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science</t>
+          <t>School of Architecture and Urban Planning</t>
         </is>
       </c>
       <c r="E64" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science</t>
+          <t/>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="0">
         <is>
-          <t>Hao Wang</t>
+          <t>Chisheng Wang</t>
         </is>
       </c>
       <c r="G64" t="inlineStr" s="0">
@@ -8127,12 +8127,12 @@
       </c>
       <c r="H64" t="inlineStr" s="0">
         <is>
-          <t>wanghao.cs@whu.edu.cn</t>
+          <t>wangchisheng@szu.edu.cn</t>
         </is>
       </c>
       <c r="I64" t="inlineStr" s="0">
         <is>
-          <t>https://jszy.whu.edu.cn/wanghao6/en/index.htm</t>
+          <t/>
         </is>
       </c>
       <c r="J64" t="inlineStr" s="0">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="K64" t="inlineStr" s="0">
         <is>
-          <t>spatiotemporal data management; interactive learning; recommender systems</t>
+          <t>remote sensing image processing and smart city development</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="0">
         <is>
-          <t>spatiotemporal data; interactive learning; recommender systems</t>
+          <t>remote sensing; image processing; smart city</t>
         </is>
       </c>
       <c r="M64" t="inlineStr" s="0">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="P64" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R64" t="inlineStr" s="0">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="S64" t="inlineStr" s="0">
         <is>
-          <t>Not contacted</t>
+          <t>Contacted</t>
         </is>
       </c>
       <c r="T64" t="inlineStr" s="0">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="V64" t="inlineStr" s="0">
         <is>
-          <t>https://jszy.whu.edu.cn/wanghao6/en/index.htm</t>
+          <t/>
         </is>
       </c>
       <c r="W64" t="inlineStr" s="0">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="X64" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official Wuhan University faculty profile</t>
+          <t>Imported from local workbook Shenzhen University.xlsx; progress noted as 1st Email Done</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr" s="0">
@@ -8219,32 +8219,32 @@
     <row r="65">
       <c r="A65" t="inlineStr" s="0">
         <is>
-          <t>HUST-CS-001</t>
+          <t>SZU-003</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="0">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Shenzhen University</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="0">
         <is>
-          <t>985_non_C9</t>
+          <t>other</t>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>College of Computer Science and Software Engineering</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t/>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="0">
         <is>
-          <t>Jin Renchao</t>
+          <t>Victor Chung Ming Leung</t>
         </is>
       </c>
       <c r="G65" t="inlineStr" s="0">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H65" t="inlineStr" s="0">
         <is>
-          <t>jrc@hust.edu.cn</t>
+          <t>vleung@ieee.org</t>
         </is>
       </c>
       <c r="I65" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1446/1433.htm</t>
+          <t/>
         </is>
       </c>
       <c r="J65" t="inlineStr" s="0">
@@ -8269,12 +8269,12 @@
       </c>
       <c r="K65" t="inlineStr" s="0">
         <is>
-          <t>Artificial intelligence; medical image processing and analysis; computer vision</t>
+          <t>mobile computing; intelligent networking; artificial intelligence</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="0">
         <is>
-          <t>artificial intelligence; medical image analysis; computer vision</t>
+          <t>mobile computing; intelligent networking; artificial intelligence</t>
         </is>
       </c>
       <c r="M65" t="inlineStr" s="0">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="P65" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R65" t="inlineStr" s="0">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="V65" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1446/1433.htm</t>
+          <t/>
         </is>
       </c>
       <c r="W65" t="inlineStr" s="0">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="X65" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official HUST faculty profile</t>
+          <t>Imported from local workbook Shenzhen University.xlsx; user-curated professor list</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr" s="0">
@@ -8346,32 +8346,32 @@
     <row r="66">
       <c r="A66" t="inlineStr" s="0">
         <is>
-          <t>HUST-CS-002</t>
+          <t>HITSZ-001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="0">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Harbin Institute of Technology</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="0">
         <is>
-          <t>985_non_C9</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="D66" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>School of Energy Science and Engineering</t>
         </is>
       </c>
       <c r="E66" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>HIT Shenzhen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="0">
         <is>
-          <t>Chen Jincai</t>
+          <t>Shuai Yong</t>
         </is>
       </c>
       <c r="G66" t="inlineStr" s="0">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="H66" t="inlineStr" s="0">
         <is>
-          <t>jcchen@hust.edu.cn</t>
+          <t>shuaiyong@hit.edu.cn</t>
         </is>
       </c>
       <c r="I66" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1464/1187.htm</t>
+          <t/>
         </is>
       </c>
       <c r="J66" t="inlineStr" s="0">
@@ -8396,12 +8396,12 @@
       </c>
       <c r="K66" t="inlineStr" s="0">
         <is>
-          <t>New memory theory and technology; big data storage and analysis; machine learning; image processing</t>
+          <t/>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="0">
         <is>
-          <t>new memory; big data; machine learning; image processing</t>
+          <t/>
         </is>
       </c>
       <c r="M66" t="inlineStr" s="0">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="P66" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R66" t="inlineStr" s="0">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="S66" t="inlineStr" s="0">
         <is>
-          <t>Not contacted</t>
+          <t>Contacted</t>
         </is>
       </c>
       <c r="T66" t="inlineStr" s="0">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="V66" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1464/1187.htm</t>
+          <t/>
         </is>
       </c>
       <c r="W66" t="inlineStr" s="0">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="X66" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official HUST faculty profile</t>
+          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen; progress noted as 1st email</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr" s="0">
@@ -8473,47 +8473,47 @@
     <row r="67">
       <c r="A67" t="inlineStr" s="0">
         <is>
-          <t>HUST-CS-003</t>
+          <t>HITSZ-002</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="0">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Harbin Institute of Technology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="0">
         <is>
-          <t>985_non_C9</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="D67" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>School of Energy Science and Engineering</t>
         </is>
       </c>
       <c r="E67" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>HIT Shenzhen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="0">
         <is>
-          <t>Hu Long</t>
+          <t>Yu Daren</t>
         </is>
       </c>
       <c r="G67" t="inlineStr" s="0">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr" s="0">
         <is>
-          <t>hulong@hust.edu.cn</t>
+          <t>yudaren@hit.edu.cn</t>
         </is>
       </c>
       <c r="I67" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1724/1427.htm</t>
+          <t/>
         </is>
       </c>
       <c r="J67" t="inlineStr" s="0">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="K67" t="inlineStr" s="0">
         <is>
-          <t>Emotional computing; edge computing; software defined network; big data</t>
+          <t/>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="0">
         <is>
-          <t>emotional computing; edge computing; SDN; big data</t>
+          <t/>
         </is>
       </c>
       <c r="M67" t="inlineStr" s="0">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="Q67" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R67" t="inlineStr" s="0">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="V67" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1724/1427.htm</t>
+          <t/>
         </is>
       </c>
       <c r="W67" t="inlineStr" s="0">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="X67" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official HUST faculty profile</t>
+          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr" s="0">
@@ -8600,47 +8600,47 @@
     <row r="68">
       <c r="A68" t="inlineStr" s="0">
         <is>
-          <t>HUST-CS-004</t>
+          <t>HITSZ-003</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="0">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Harbin Institute of Technology</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="0">
         <is>
-          <t>985_non_C9</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>School of Energy Science and Engineering</t>
         </is>
       </c>
       <c r="E68" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>HIT Shenzhen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="0">
         <is>
-          <t>Wei Wei</t>
+          <t>Liu Jinfu</t>
         </is>
       </c>
       <c r="G68" t="inlineStr" s="0">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr" s="0">
         <is>
-          <t>weiw@hust.edu.cn</t>
+          <t>jinfuliu@hit.edu.cn</t>
         </is>
       </c>
       <c r="I68" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1553/1661.htm</t>
+          <t/>
         </is>
       </c>
       <c r="J68" t="inlineStr" s="0">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="K68" t="inlineStr" s="0">
         <is>
-          <t>Artificial intelligence; natural language processing; information retrieval; textual data mining; recommendation systems; deep learning</t>
+          <t>modeling; control; early warning; diagnosis; intelligent maintenance of power systems; new energy; energy internet; integrated smart energy</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="0">
         <is>
-          <t>artificial intelligence; NLP; IR; data mining; recommender systems; deep learning</t>
+          <t>modeling; control; diagnosis; smart maintenance; new energy; energy internet</t>
         </is>
       </c>
       <c r="M68" t="inlineStr" s="0">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="P68" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr" s="0">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R68" t="inlineStr" s="0">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="V68" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1553/1661.htm</t>
+          <t/>
         </is>
       </c>
       <c r="W68" t="inlineStr" s="0">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="X68" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official HUST faculty profile</t>
+          <t>Imported from local workbook Shenzhen University.xlsx under HIT Shenzhen</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr" s="0">
@@ -8727,12 +8727,12 @@
     <row r="69">
       <c r="A69" t="inlineStr" s="0">
         <is>
-          <t>HUST-CS-005</t>
+          <t>WHU-CS-001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="0">
         <is>
-          <t>Huazhong University of Science and Technology</t>
+          <t>Wuhan University</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="0">
@@ -8742,32 +8742,32 @@
       </c>
       <c r="D69" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>School of Computer Science</t>
         </is>
       </c>
       <c r="E69" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>School of Computer Science</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="0">
         <is>
-          <t>Gu Lin</t>
+          <t>Sheng Wang</t>
         </is>
       </c>
       <c r="G69" t="inlineStr" s="0">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr" s="0">
         <is>
-          <t>lingu@hust.edu.cn</t>
+          <t/>
         </is>
       </c>
       <c r="I69" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1319/1196.htm</t>
+          <t>https://sheng.whu.edu.cn/</t>
         </is>
       </c>
       <c r="J69" t="inlineStr" s="0">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="K69" t="inlineStr" s="0">
         <is>
-          <t>Cloud native; serverless computing; microservice; edge computing</t>
+          <t>Multi-model database theory and systems</t>
         </is>
       </c>
       <c r="L69" t="inlineStr" s="0">
         <is>
-          <t>cloud native; serverless; microservices; edge computing</t>
+          <t>multi-model databases; systems; data markets; scientific discovery</t>
         </is>
       </c>
       <c r="M69" t="inlineStr" s="0">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="P69" t="inlineStr" s="0">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr" s="0">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="V69" t="inlineStr" s="0">
         <is>
-          <t>https://en-cs.hust.edu.cn/info/1319/1196.htm</t>
+          <t>https://sheng.whu.edu.cn/</t>
         </is>
       </c>
       <c r="W69" t="inlineStr" s="0">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="X69" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official HUST faculty profile</t>
+          <t>Extracted from official WHU personal page on whu.edu.cn domain</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr" s="0">
@@ -8854,12 +8854,12 @@
     <row r="70">
       <c r="A70" t="inlineStr" s="0">
         <is>
-          <t>TJU-CS-001</t>
+          <t>WHU-CS-002</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="0">
         <is>
-          <t>Tianjin University</t>
+          <t>Wuhan University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="0">
@@ -8869,47 +8869,47 @@
       </c>
       <c r="D70" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>School of Computer Science</t>
         </is>
       </c>
       <c r="E70" t="inlineStr" s="0">
         <is>
-          <t>School of Computer Science and Technology</t>
+          <t>School of Computer Science</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="0">
         <is>
-          <t>Bo Wang</t>
+          <t>Hao Wang</t>
         </is>
       </c>
       <c r="G70" t="inlineStr" s="0">
         <is>
-          <t>Associate Professor</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr" s="0">
         <is>
-          <t>B_o_wang@tju.edu.cn</t>
+          <t>wanghao.cs@whu.edu.cn</t>
         </is>
       </c>
       <c r="I70" t="inlineStr" s="0">
         <is>
-          <t>https://tiei.tju.edu.cn/info/1614/3494.htm</t>
+          <t>https://jszy.whu.edu.cn/wanghao6/en/index.htm</t>
         </is>
       </c>
       <c r="J70" t="inlineStr" s="0">
         <is>
-          <t>http://cs.tju.edu.cn/faculty/wangbo/index.htm</t>
+          <t/>
         </is>
       </c>
       <c r="K70" t="inlineStr" s="0">
         <is>
-          <t>Intelligent dialog systems; computational psychology; personalized recommendation; natural language processing</t>
+          <t>spatiotemporal data management; interactive learning; recommender systems</t>
         </is>
       </c>
       <c r="L70" t="inlineStr" s="0">
         <is>
-          <t>intelligent dialog; computational psychology; recommendation; NLP</t>
+          <t>spatiotemporal data; interactive learning; recommender systems</t>
         </is>
       </c>
       <c r="M70" t="inlineStr" s="0">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="P70" t="inlineStr" s="0">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr" s="0">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="V70" t="inlineStr" s="0">
         <is>
-          <t>https://tiei.tju.edu.cn/info/1614/3494.htm</t>
+          <t>https://jszy.whu.edu.cn/wanghao6/en/index.htm</t>
         </is>
       </c>
       <c r="W70" t="inlineStr" s="0">
@@ -8969,7 +8969,7 @@
       </c>
       <c r="X70" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official Tianjin University profile</t>
+          <t>Extracted from official Wuhan University faculty profile</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr" s="0">
@@ -8981,12 +8981,12 @@
     <row r="71">
       <c r="A71" t="inlineStr" s="0">
         <is>
-          <t>TJU-CS-002</t>
+          <t>HUST-CS-001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="0">
         <is>
-          <t>Tianjin University</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="0">
@@ -8996,17 +8996,17 @@
       </c>
       <c r="D71" t="inlineStr" s="0">
         <is>
-          <t>College of Intelligence and Computing</t>
+          <t>School of Computer Science and Technology</t>
         </is>
       </c>
       <c r="E71" t="inlineStr" s="0">
         <is>
-          <t>College of Intelligence and Computing</t>
+          <t>School of Computer Science and Technology</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="0">
         <is>
-          <t>Kun Li</t>
+          <t>Jin Renchao</t>
         </is>
       </c>
       <c r="G71" t="inlineStr" s="0">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="H71" t="inlineStr" s="0">
         <is>
-          <t>lik@tju.edu.cn</t>
+          <t>jrc@hust.edu.cn</t>
         </is>
       </c>
       <c r="I71" t="inlineStr" s="0">
         <is>
-          <t>https://cic.tju.edu.cn/faculty/likun/bio.html</t>
+          <t>https://en-cs.hust.edu.cn/info/1446/1433.htm</t>
         </is>
       </c>
       <c r="J71" t="inlineStr" s="0">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="K71" t="inlineStr" s="0">
         <is>
-          <t>3D vision and digital humans</t>
+          <t>Artificial intelligence; medical image processing and analysis; computer vision</t>
         </is>
       </c>
       <c r="L71" t="inlineStr" s="0">
         <is>
-          <t>3D vision; digital humans; computer vision</t>
+          <t>artificial intelligence; medical image analysis; computer vision</t>
         </is>
       </c>
       <c r="M71" t="inlineStr" s="0">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="P71" t="inlineStr" s="0">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr" s="0">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="V71" t="inlineStr" s="0">
         <is>
-          <t>https://cic.tju.edu.cn/faculty/likun/bio.html</t>
+          <t>https://en-cs.hust.edu.cn/info/1446/1433.htm</t>
         </is>
       </c>
       <c r="W71" t="inlineStr" s="0">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="X71" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official Tianjin University faculty profile</t>
+          <t>Extracted from official HUST faculty profile</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr" s="0">
@@ -9108,12 +9108,12 @@
     <row r="72">
       <c r="A72" t="inlineStr" s="0">
         <is>
-          <t>TJU-CS-003</t>
+          <t>HUST-CS-002</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="0">
         <is>
-          <t>Tianjin University</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="0">
@@ -9123,17 +9123,17 @@
       </c>
       <c r="D72" t="inlineStr" s="0">
         <is>
-          <t>College of Intelligence and Computing</t>
+          <t>School of Computer Science and Technology</t>
         </is>
       </c>
       <c r="E72" t="inlineStr" s="0">
         <is>
-          <t>College of Intelligence and Computing</t>
+          <t>School of Computer Science and Technology</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="0">
         <is>
-          <t>Guangquan Xu</t>
+          <t>Chen Jincai</t>
         </is>
       </c>
       <c r="G72" t="inlineStr" s="0">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="H72" t="inlineStr" s="0">
         <is>
-          <t>losin@tju.edu.cn</t>
+          <t>jcchen@hust.edu.cn</t>
         </is>
       </c>
       <c r="I72" t="inlineStr" s="0">
         <is>
-          <t>https://cic.tju.edu.cn/faculty/xugq/index.htm</t>
+          <t>https://en-cs.hust.edu.cn/info/1464/1187.htm</t>
         </is>
       </c>
       <c r="J72" t="inlineStr" s="0">
@@ -9158,12 +9158,12 @@
       </c>
       <c r="K72" t="inlineStr" s="0">
         <is>
-          <t>Network security and intelligent monitoring</t>
+          <t>New memory theory and technology; big data storage and analysis; machine learning; image processing</t>
         </is>
       </c>
       <c r="L72" t="inlineStr" s="0">
         <is>
-          <t>network security; intelligent monitoring; software engineering</t>
+          <t>new memory; big data; machine learning; image processing</t>
         </is>
       </c>
       <c r="M72" t="inlineStr" s="0">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="P72" t="inlineStr" s="0">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr" s="0">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="V72" t="inlineStr" s="0">
         <is>
-          <t>https://cic.tju.edu.cn/faculty/xugq/index.htm</t>
+          <t>https://en-cs.hust.edu.cn/info/1464/1187.htm</t>
         </is>
       </c>
       <c r="W72" t="inlineStr" s="0">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="X72" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official Tianjin University faculty profile</t>
+          <t>Extracted from official HUST faculty profile</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr" s="0">
@@ -9235,12 +9235,12 @@
     <row r="73">
       <c r="A73" t="inlineStr" s="0">
         <is>
-          <t>TONGJI-001</t>
+          <t>HUST-CS-003</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="0">
         <is>
-          <t>Tongji University</t>
+          <t>Huazhong University of Science and Technology</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="0">
@@ -9250,47 +9250,47 @@
       </c>
       <c r="D73" t="inlineStr" s="0">
         <is>
-          <t>Department of Control Science and Engineering</t>
+          <t>School of Computer Science and Technology</t>
         </is>
       </c>
       <c r="E73" t="inlineStr" s="0">
         <is>
-          <t>College of Electronic and Information Engineering</t>
+          <t>School of Computer Science and Technology</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="0">
         <is>
-          <t>Shi Miaojing</t>
+          <t>Hu Long</t>
         </is>
       </c>
       <c r="G73" t="inlineStr" s="0">
         <is>
-          <t>Professor</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr" s="0">
         <is>
-          <t>mshi@tongji.edu.cn</t>
+          <t>hulong@hust.edu.cn</t>
         </is>
       </c>
       <c r="I73" t="inlineStr" s="0">
         <is>
-          <t>https://see-en.tongji.edu.cn/info/1016/1522.htm</t>
+          <t>https://en-cs.hust.edu.cn/info/1724/1427.htm</t>
         </is>
       </c>
       <c r="J73" t="inlineStr" s="0">
         <is>
-          <t>https://sites.google.com/site/miaojingshi/</t>
+          <t/>
         </is>
       </c>
       <c r="K73" t="inlineStr" s="0">
         <is>
-          <t>Computer vision; machine learning; multimedia computing</t>
+          <t>Emotional computing; edge computing; software defined network; big data</t>
         </is>
       </c>
       <c r="L73" t="inlineStr" s="0">
         <is>
-          <t>computer vision; machine learning; multimedia computing</t>
+          <t>emotional computing; edge computing; SDN; big data</t>
         </is>
       </c>
       <c r="M73" t="inlineStr" s="0">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="V73" t="inlineStr" s="0">
         <is>
-          <t>https://see-en.tongji.edu.cn/info/1016/1522.htm</t>
+          <t>https://en-cs.hust.edu.cn/info/1724/1427.htm</t>
         </is>
       </c>
       <c r="W73" t="inlineStr" s="0">
@@ -9350,7 +9350,7 @@
       </c>
       <c r="X73" t="inlineStr" s="0">
         <is>
-          <t>Extracted from official Tongji faculty profile</t>
+          <t>Extracted from official HUST faculty profile</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr" s="0">
@@ -9362,125 +9362,887 @@
     <row r="74">
       <c r="A74" t="inlineStr" s="0">
         <is>
+          <t>HUST-CS-004</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr" s="0">
+        <is>
+          <t>Wei Wei</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr" s="0">
+        <is>
+          <t>weiw@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1553/1661.htm</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr" s="0">
+        <is>
+          <t>Artificial intelligence; natural language processing; information retrieval; textual data mining; recommendation systems; deep learning</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr" s="0">
+        <is>
+          <t>artificial intelligence; NLP; IR; data mining; recommender systems; deep learning</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1553/1661.htm</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HUST faculty profile</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr" s="0">
+        <is>
+          <t>HUST-CS-005</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr" s="0">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr" s="0">
+        <is>
+          <t>Gu Lin</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr" s="0">
+        <is>
+          <t>lingu@hust.edu.cn</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1319/1196.htm</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr" s="0">
+        <is>
+          <t>Cloud native; serverless computing; microservice; edge computing</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr" s="0">
+        <is>
+          <t>cloud native; serverless; microservices; edge computing</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr" s="0">
+        <is>
+          <t>https://en-cs.hust.edu.cn/info/1319/1196.htm</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official HUST faculty profile</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr" s="0">
+        <is>
+          <t>TJU-CS-001</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr" s="0">
+        <is>
+          <t>School of Computer Science and Technology</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr" s="0">
+        <is>
+          <t>Bo Wang</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr" s="0">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr" s="0">
+        <is>
+          <t>B_o_wang@tju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr" s="0">
+        <is>
+          <t>https://tiei.tju.edu.cn/info/1614/3494.htm</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr" s="0">
+        <is>
+          <t>http://cs.tju.edu.cn/faculty/wangbo/index.htm</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr" s="0">
+        <is>
+          <t>Intelligent dialog systems; computational psychology; personalized recommendation; natural language processing</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr" s="0">
+        <is>
+          <t>intelligent dialog; computational psychology; recommendation; NLP</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr" s="0">
+        <is>
+          <t>https://tiei.tju.edu.cn/info/1614/3494.htm</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tianjin University profile</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr" s="0">
+        <is>
+          <t>TJU-CS-002</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr" s="0">
+        <is>
+          <t>Kun Li</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr" s="0">
+        <is>
+          <t>lik@tju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/likun/bio.html</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr" s="0">
+        <is>
+          <t>3D vision and digital humans</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr" s="0">
+        <is>
+          <t>3D vision; digital humans; computer vision</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/likun/bio.html</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tianjin University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr" s="0">
+        <is>
+          <t>TJU-CS-003</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr" s="0">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr" s="0">
+        <is>
+          <t>College of Intelligence and Computing</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr" s="0">
+        <is>
+          <t>Guangquan Xu</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr" s="0">
+        <is>
+          <t>losin@tju.edu.cn</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/xugq/index.htm</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr" s="0">
+        <is>
+          <t>Network security and intelligent monitoring</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr" s="0">
+        <is>
+          <t>network security; intelligent monitoring; software engineering</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr" s="0">
+        <is>
+          <t>https://cic.tju.edu.cn/faculty/xugq/index.htm</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tianjin University faculty profile</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr" s="0">
+        <is>
+          <t>TONGJI-001</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr" s="0">
+        <is>
+          <t>Tongji University</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr" s="0">
+        <is>
+          <t>985_non_C9</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="0">
+        <is>
+          <t>Department of Control Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr" s="0">
+        <is>
+          <t>College of Electronic and Information Engineering</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr" s="0">
+        <is>
+          <t>Shi Miaojing</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr" s="0">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr" s="0">
+        <is>
+          <t>mshi@tongji.edu.cn</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr" s="0">
+        <is>
+          <t>https://see-en.tongji.edu.cn/info/1016/1522.htm</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr" s="0">
+        <is>
+          <t>https://sites.google.com/site/miaojingshi/</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr" s="0">
+        <is>
+          <t>Computer vision; machine learning; multimedia computing</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr" s="0">
+        <is>
+          <t>computer vision; machine learning; multimedia computing</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr" s="0">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr" s="0">
+        <is>
+          <t>Not contacted</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr" s="0">
+        <is>
+          <t>No response</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr" s="0">
+        <is>
+          <t>https://see-en.tongji.edu.cn/info/1016/1522.htm</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr" s="0">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr" s="0">
+        <is>
+          <t>Extracted from official Tongji faculty profile</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr" s="0">
+        <is>
           <t>SYSU-001</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr" s="0">
+      <c r="B80" t="inlineStr" s="0">
         <is>
           <t>Sun Yat-sen University</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr" s="0">
+      <c r="C80" t="inlineStr" s="0">
         <is>
           <t>985_non_C9</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr" s="0">
+      <c r="D80" t="inlineStr" s="0">
         <is>
           <t>School of Computer Science and Engineering</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr" s="0">
+      <c r="E80" t="inlineStr" s="0">
         <is>
           <t>School of Computer Science and Engineering</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr" s="0">
+      <c r="F80" t="inlineStr" s="0">
         <is>
           <t>Li Wenjun</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr" s="0">
+      <c r="G80" t="inlineStr" s="0">
         <is>
           <t>Professor</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr" s="0">
+      <c r="H80" t="inlineStr" s="0">
         <is>
           <t>lnslwj@mail.sysu.edu.cn</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr" s="0">
+      <c r="I80" t="inlineStr" s="0">
         <is>
           <t>https://cse.sysu.edu.cn/en/teacher/LiWenjun</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr" s="0">
+      <c r="J80" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr" s="0">
         <is>
           <t>Computer science and software systems</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr" s="0">
+      <c r="L80" t="inlineStr" s="0">
         <is>
           <t>computer science; software systems</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr" s="0">
+      <c r="M80" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr" s="0">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr" s="0">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr" s="0">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr" s="0">
+      <c r="Q80" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr" s="0">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr" s="0">
         <is>
           <t>Not contacted</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr" s="0">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr" s="0">
+      <c r="T80" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr" s="0">
         <is>
           <t>No response</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr" s="0">
+      <c r="V80" t="inlineStr" s="0">
         <is>
           <t>https://cse.sysu.edu.cn/en/teacher/LiWenjun</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr" s="0">
+      <c r="W80" t="inlineStr" s="0">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr" s="0">
+      <c r="X80" t="inlineStr" s="0">
         <is>
           <t>Extracted from official SYSU faculty profile</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr" s="0">
+      <c r="Y80" t="inlineStr" s="0">
         <is>
           <t/>
         </is>

--- a/workbooks/professor_master.xlsx
+++ b/workbooks/professor_master.xlsx
@@ -27,8 +27,8 @@
   <dc:title>Professor Master</dc:title>
   <dc:creator>Codex</dc:creator>
   <cp:lastModifiedBy>Codex</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:41:37Z</dcterms:modified>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-03-14T05:57:18Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-03-14T05:57:18Z</dcterms:modified>
 </cp:coreProperties>
 </file>
 
